--- a/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-[번호미정]_기록인계대장_초안.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-[번호미정]_기록인계대장_초안.xlsx
@@ -1367,7 +1367,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="95" t="inlineStr">
         <is>
-          <t>작성 안내: 현장 기록은 작성 후 3일(달력일) 이내 스캔하여 서버에 저장하고, 스캔 후 3일(달력일) 이내 종이 원본을 품질팀에 인계합니다. 인계자·인수자가 서명합니다. 기한 초과 시 사유를 비고에 기록합니다.</t>
+          <t>작성 안내: 현장 기록은 작성 후 3일(달력일) 이내 스캔하여 서버에 저장하고, 스캔 후 3일(달력일) 이내 종이 원본을 품질팀에 인계합니다. 인계자·인수자가 서명합니다. 기한 초과 시 사유를 비고에 기록합니다. 스캔 불일치·판독 불가 시 비고에 '보류'로 기록하고, 3일(달력일) 이내 재스캔하여 일치가 확인되면 비고에 '보류 해제(일자)'를 기록합니다.</t>
         </is>
       </c>
       <c r="B23" s="96" t="n"/>

--- a/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-[번호미정]_기록인계대장_초안.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-[번호미정]_기록인계대장_초안.xlsx
@@ -1367,7 +1367,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="95" t="inlineStr">
         <is>
-          <t>작성 안내: 현장 기록은 작성 후 3일(달력일) 이내 스캔하여 서버에 저장하고, 스캔 후 3일(달력일) 이내 종이 원본을 품질팀에 인계합니다. 인계자·인수자가 서명합니다. 기한 초과 시 사유를 비고에 기록합니다. 스캔 불일치·판독 불가 시 비고에 '보류'로 기록하고, 3일(달력일) 이내 재스캔하여 일치가 확인되면 비고에 '보류 해제(일자)'를 기록합니다.</t>
+          <t>작성 안내: 현장 기록은 작성 후 3일(달력일) 이내 스캔하여 서버에 저장하고, 스캔 후 3일(달력일) 이내 종이 원본을 품질팀에 인계합니다. 인계자·인수자가 서명합니다. 기한 초과 시 사유를 비고에 기록합니다. 스캔 불일치·판독 불가 시 비고에 '보류'로 기록하고, 3일(달력일) 이내 재스캔하여 일치가 확인되면 비고에 '보류 해제(일자)'를 기록합니다. 긴급 추적(고객 클레임·리콜·제품안전)으로 보류 기록의 종이 원본을 활용할 때는 품질책임자가 비고에 승인 일자와 서명을 기록합니다.</t>
         </is>
       </c>
       <c r="B23" s="96" t="n"/>

--- a/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-[번호미정]_기록인계대장_초안.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/03_EDIT/AUTO_DRAFT/SH-FM-[번호미정]_기록인계대장_초안.xlsx
@@ -1,11 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="인계대장_초안" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인계대장_초안" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'인계대장_초안'!$A$1:$F$32</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -1087,7 +1089,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1527,6 +1529,8 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>